--- a/static/planilhas/dados_inss.xlsx
+++ b/static/planilhas/dados_inss.xlsx
@@ -413,98 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Razão Social</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Valor Total do Documento</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Código de Barras</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Vencimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>62.576.830/0001-19 CONDOMINIO EDIFICIO JULIANA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7.902,17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>85840000079 5 02170385260 7 51071626043 2 09680664014 0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>07.022.952/0001-55 CONDOMINIO DO EDIFICIO RESIDENCIAL QUINTELA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.375,55</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>85810000023 4 75550385260 2 51071626043 2 12888459864 7</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>68.760.388/0001-62 CONDOMINIO DO EDIFICIO SABIN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3.655,60</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>85800000036 4 55600385260 9 51071626044 0 60561822402 4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>